--- a/diseases/d099/1995-1999.xlsx
+++ b/diseases/d099/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -22022,7 +22022,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24422,7 +24422,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -26822,7 +26822,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -27622,7 +27622,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -28422,7 +28422,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -29222,7 +29222,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -30022,7 +30022,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -30822,7 +30822,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -33051,7 +33051,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33851,7 +33851,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34651,7 +34651,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -35451,7 +35451,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -36251,7 +36251,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -37051,7 +37051,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37851,7 +37851,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -38651,7 +38651,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -39451,7 +39451,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -41051,7 +41051,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -42719,7 +42719,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -43758,7 +43758,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -44797,7 +44797,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -45836,7 +45836,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -46875,7 +46875,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -47914,7 +47914,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -48953,7 +48953,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -49992,7 +49992,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -51031,7 +51031,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -52070,7 +52070,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -53109,7 +53109,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -54148,7 +54148,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">

--- a/diseases/d099/1995-1999.xlsx
+++ b/diseases/d099/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -22022,7 +22022,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24422,7 +24422,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -26822,7 +26822,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -27622,7 +27622,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -28422,7 +28422,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -29222,7 +29222,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -30022,7 +30022,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -30822,7 +30822,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -33051,7 +33051,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33851,7 +33851,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34651,7 +34651,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -35451,7 +35451,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -36251,7 +36251,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -37051,7 +37051,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37851,7 +37851,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -38651,7 +38651,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -39451,7 +39451,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -41051,7 +41051,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -42719,7 +42719,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -43758,7 +43758,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -44797,7 +44797,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -45836,7 +45836,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -46875,7 +46875,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -47914,7 +47914,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -48953,7 +48953,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -49992,7 +49992,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -51031,7 +51031,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -52070,7 +52070,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -53109,7 +53109,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -54148,7 +54148,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
